--- a/fcr-generator/inspection_report_706271_D01_mock.xlsx
+++ b/fcr-generator/inspection_report_706271_D01_mock.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Z005BYAE\Documents\fcr_ws\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Z005BYAE\Documents\fcr_ws\fcr-generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3BEC6B-B5F0-4A1A-A858-A951734ECA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC99AF3-59E5-4220-A2B0-353B2DC710B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,15 +75,6 @@
     <t>测试和安装单据需要填写的信息的完整性和正确性</t>
   </si>
   <si>
-    <t>HZ-478-M706271-B06</t>
-  </si>
-  <si>
-    <t>706271</t>
-  </si>
-  <si>
-    <t>31302675</t>
-  </si>
-  <si>
     <t>Q0+W80+Q1+T1+Q52+T2</t>
   </si>
   <si>
@@ -249,9 +240,6 @@
     <t>2026-09-09 05:57:26 +0000 UTC</t>
   </si>
   <si>
-    <t>HZ-478-M706271-B07</t>
-  </si>
-  <si>
     <t>单据信息不完整。</t>
   </si>
   <si>
@@ -301,6 +289,18 @@
   </si>
   <si>
     <t>Q8+Q9+W1</t>
+  </si>
+  <si>
+    <t>mock_drawing_page_1</t>
+  </si>
+  <si>
+    <t>mock_drawing_page_2</t>
+  </si>
+  <si>
+    <t>mock_proj_id</t>
+  </si>
+  <si>
+    <t>mock_b_id</t>
   </si>
 </sst>
 </file>
@@ -702,28 +702,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -734,31 +737,28 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -769,28 +769,28 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -801,31 +801,28 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -836,31 +833,28 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -871,28 +865,28 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -903,28 +897,28 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -935,28 +929,28 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,28 +961,28 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -999,31 +993,28 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1034,28 +1025,28 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1066,28 +1057,28 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1098,28 +1089,28 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1130,28 +1121,28 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1162,28 +1153,28 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1194,28 +1185,28 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1226,31 +1217,28 @@
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1261,31 +1249,28 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
         <v>87</v>
       </c>
       <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" t="s">
         <v>16</v>
       </c>
-      <c r="H19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" t="s">
-        <v>24</v>
-      </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1296,31 +1281,28 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J20" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1331,31 +1313,28 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1366,31 +1345,28 @@
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K22" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1401,31 +1377,28 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K23" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1436,31 +1409,28 @@
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1471,31 +1441,28 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" t="s">
         <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K25" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1506,28 +1473,28 @@
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1538,31 +1505,28 @@
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" t="s">
         <v>87</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J27" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K27" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1573,28 +1537,28 @@
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1605,28 +1569,28 @@
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1637,31 +1601,28 @@
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" t="s">
         <v>87</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K30" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1672,28 +1633,28 @@
         <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1704,28 +1665,28 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1736,28 +1697,28 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" t="s">
         <v>86</v>
       </c>
-      <c r="D33" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" t="s">
-        <v>75</v>
-      </c>
       <c r="J33" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1768,28 +1729,28 @@
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1800,28 +1761,31 @@
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1832,28 +1796,31 @@
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1864,28 +1831,31 @@
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I37" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1896,28 +1866,31 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s">
+        <v>90</v>
+      </c>
+      <c r="I38" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K38" t="s">
         <v>34</v>
-      </c>
-      <c r="E38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" t="s">
-        <v>89</v>
-      </c>
-      <c r="J38" t="s">
-        <v>36</v>
-      </c>
-      <c r="K38" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1928,28 +1901,31 @@
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J39" t="s">
         <v>40</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -1960,28 +1936,31 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
         <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F40" t="s">
+        <v>83</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J40" t="s">
         <v>43</v>
       </c>
       <c r="K40" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -1992,28 +1971,28 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
         <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J41" t="s">
         <v>46</v>
       </c>
       <c r="K41" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2024,28 +2003,31 @@
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
         <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K42" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2056,28 +2038,28 @@
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J43" t="s">
         <v>53</v>
       </c>
       <c r="K43" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2088,28 +2070,28 @@
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D44" t="s">
         <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J44" t="s">
         <v>56</v>
       </c>
       <c r="K44" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,28 +2102,31 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
         <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="F45" t="s">
+        <v>83</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J45" t="s">
         <v>59</v>
       </c>
       <c r="K45" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2152,28 +2137,28 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
         <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J46" t="s">
         <v>62</v>
       </c>
       <c r="K46" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2184,28 +2169,28 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
         <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J47" t="s">
         <v>65</v>
       </c>
       <c r="K47" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2216,28 +2201,28 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J48" t="s">
         <v>68</v>
       </c>
       <c r="K48" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2248,28 +2233,28 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" t="s">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I49" t="s">
         <v>15</v>
       </c>
-      <c r="G49" t="s">
+      <c r="J49" t="s">
         <v>16</v>
       </c>
-      <c r="H49" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" t="s">
-        <v>89</v>
-      </c>
-      <c r="J49" t="s">
-        <v>71</v>
-      </c>
       <c r="K49" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2280,28 +2265,31 @@
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
+        <v>87</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s">
+        <v>90</v>
+      </c>
+      <c r="I50" t="s">
         <v>15</v>
       </c>
-      <c r="G50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" t="s">
-        <v>90</v>
-      </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2312,28 +2300,28 @@
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s">
+        <v>90</v>
+      </c>
+      <c r="I51" t="s">
         <v>15</v>
       </c>
-      <c r="G51" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" t="s">
-        <v>90</v>
-      </c>
       <c r="J51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2350,22 +2338,25 @@
         <v>27</v>
       </c>
       <c r="E52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s">
+        <v>90</v>
+      </c>
+      <c r="I52" t="s">
         <v>15</v>
       </c>
-      <c r="G52" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52" t="s">
-        <v>17</v>
-      </c>
-      <c r="I52" t="s">
-        <v>90</v>
-      </c>
       <c r="J52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K52" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2376,28 +2367,31 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" t="s">
         <v>15</v>
       </c>
-      <c r="G53" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I53" t="s">
-        <v>90</v>
-      </c>
       <c r="J53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K53" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2408,28 +2402,28 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s">
+        <v>90</v>
+      </c>
+      <c r="I54" t="s">
         <v>15</v>
       </c>
-      <c r="G54" t="s">
-        <v>16</v>
-      </c>
-      <c r="H54" t="s">
-        <v>17</v>
-      </c>
-      <c r="I54" t="s">
-        <v>90</v>
-      </c>
       <c r="J54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K54" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2446,22 +2440,22 @@
         <v>39</v>
       </c>
       <c r="E55" t="s">
+        <v>87</v>
+      </c>
+      <c r="G55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s">
+        <v>90</v>
+      </c>
+      <c r="I55" t="s">
         <v>15</v>
-      </c>
-      <c r="G55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H55" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" t="s">
-        <v>90</v>
       </c>
       <c r="J55" t="s">
         <v>40</v>
       </c>
       <c r="K55" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2478,22 +2472,22 @@
         <v>42</v>
       </c>
       <c r="E56" t="s">
+        <v>87</v>
+      </c>
+      <c r="G56" t="s">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s">
+        <v>90</v>
+      </c>
+      <c r="I56" t="s">
         <v>15</v>
-      </c>
-      <c r="G56" t="s">
-        <v>16</v>
-      </c>
-      <c r="H56" t="s">
-        <v>17</v>
-      </c>
-      <c r="I56" t="s">
-        <v>90</v>
       </c>
       <c r="J56" t="s">
         <v>43</v>
       </c>
       <c r="K56" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2510,22 +2504,22 @@
         <v>45</v>
       </c>
       <c r="E57" t="s">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s">
+        <v>90</v>
+      </c>
+      <c r="I57" t="s">
         <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>16</v>
-      </c>
-      <c r="H57" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" t="s">
-        <v>90</v>
       </c>
       <c r="J57" t="s">
         <v>46</v>
       </c>
       <c r="K57" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2542,22 +2536,25 @@
         <v>48</v>
       </c>
       <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" t="s">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s">
+        <v>90</v>
+      </c>
+      <c r="I58" t="s">
         <v>15</v>
       </c>
-      <c r="G58" t="s">
-        <v>16</v>
-      </c>
-      <c r="H58" t="s">
-        <v>17</v>
-      </c>
-      <c r="I58" t="s">
-        <v>90</v>
-      </c>
       <c r="J58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K58" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2568,28 +2565,28 @@
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" t="s">
+        <v>87</v>
+      </c>
+      <c r="G59" t="s">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s">
+        <v>90</v>
+      </c>
+      <c r="I59" t="s">
         <v>15</v>
-      </c>
-      <c r="G59" t="s">
-        <v>16</v>
-      </c>
-      <c r="H59" t="s">
-        <v>17</v>
-      </c>
-      <c r="I59" t="s">
-        <v>90</v>
       </c>
       <c r="J59" t="s">
         <v>53</v>
       </c>
       <c r="K59" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2606,22 +2603,22 @@
         <v>55</v>
       </c>
       <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G60" t="s">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s">
+        <v>90</v>
+      </c>
+      <c r="I60" t="s">
         <v>15</v>
-      </c>
-      <c r="G60" t="s">
-        <v>16</v>
-      </c>
-      <c r="H60" t="s">
-        <v>17</v>
-      </c>
-      <c r="I60" t="s">
-        <v>90</v>
       </c>
       <c r="J60" t="s">
         <v>56</v>
       </c>
       <c r="K60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2638,22 +2635,22 @@
         <v>58</v>
       </c>
       <c r="E61" t="s">
+        <v>87</v>
+      </c>
+      <c r="G61" t="s">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s">
+        <v>90</v>
+      </c>
+      <c r="I61" t="s">
         <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" t="s">
-        <v>17</v>
-      </c>
-      <c r="I61" t="s">
-        <v>90</v>
       </c>
       <c r="J61" t="s">
         <v>59</v>
       </c>
       <c r="K61" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2670,22 +2667,22 @@
         <v>61</v>
       </c>
       <c r="E62" t="s">
+        <v>87</v>
+      </c>
+      <c r="G62" t="s">
+        <v>89</v>
+      </c>
+      <c r="H62" t="s">
+        <v>90</v>
+      </c>
+      <c r="I62" t="s">
         <v>15</v>
-      </c>
-      <c r="G62" t="s">
-        <v>16</v>
-      </c>
-      <c r="H62" t="s">
-        <v>17</v>
-      </c>
-      <c r="I62" t="s">
-        <v>90</v>
       </c>
       <c r="J62" t="s">
         <v>62</v>
       </c>
       <c r="K62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2702,22 +2699,22 @@
         <v>64</v>
       </c>
       <c r="E63" t="s">
+        <v>87</v>
+      </c>
+      <c r="G63" t="s">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s">
+        <v>90</v>
+      </c>
+      <c r="I63" t="s">
         <v>15</v>
-      </c>
-      <c r="G63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H63" t="s">
-        <v>17</v>
-      </c>
-      <c r="I63" t="s">
-        <v>90</v>
       </c>
       <c r="J63" t="s">
         <v>65</v>
       </c>
       <c r="K63" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,22 +2731,22 @@
         <v>67</v>
       </c>
       <c r="E64" t="s">
+        <v>87</v>
+      </c>
+      <c r="G64" t="s">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s">
+        <v>90</v>
+      </c>
+      <c r="I64" t="s">
         <v>15</v>
-      </c>
-      <c r="G64" t="s">
-        <v>16</v>
-      </c>
-      <c r="H64" t="s">
-        <v>17</v>
-      </c>
-      <c r="I64" t="s">
-        <v>90</v>
       </c>
       <c r="J64" t="s">
         <v>68</v>
       </c>
       <c r="K64" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2763,29 +2760,36 @@
         <v>69</v>
       </c>
       <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>88</v>
+      </c>
+      <c r="F65" t="s">
         <v>70</v>
       </c>
-      <c r="E65" t="s">
-        <v>15</v>
-      </c>
       <c r="G65" t="s">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s">
+        <v>90</v>
+      </c>
+      <c r="I65" t="s">
+        <v>71</v>
+      </c>
+      <c r="J65" t="s">
         <v>16</v>
       </c>
-      <c r="H65" t="s">
-        <v>17</v>
-      </c>
-      <c r="I65" t="s">
-        <v>90</v>
-      </c>
-      <c r="J65" t="s">
-        <v>71</v>
-      </c>
       <c r="K65" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K65">
+      <sortCondition ref="E1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
